--- a/results/metrics_none.xlsx
+++ b/results/metrics_none.xlsx
@@ -572,37 +572,37 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8.729100000000001</v>
+        <v>8.400499999999999</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9.031000000000001</v>
+        <v>0.377</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>422.148</v>
+        <v>0.53</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>9.050000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>440.229</v>
+        <v>0.919</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>9.228920804459999e-06</v>
+        <v>8.35656903059e-05</v>
       </c>
       <c r="O2" s="2" t="b">
         <v>1</v>
@@ -634,37 +634,37 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>15.711</v>
+        <v>22.2544</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.535</v>
+        <v>1.257</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>972.89</v>
+        <v>25.066</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>977.425</v>
+        <v>26.346</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>100900</v>
+        <v>0.0015511402633</v>
       </c>
       <c r="O3" s="2" t="b">
         <v>1</v>
@@ -696,37 +696,37 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>13.4817</v>
+        <v>38.3948</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11.317</v>
+        <v>0.784</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1013.787</v>
+        <v>27.957</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1025.104</v>
+        <v>28.755</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>6669723.32603</v>
+        <v>4.76246515231e-06</v>
       </c>
       <c r="O4" s="2" t="b">
         <v>1</v>
@@ -758,22 +758,22 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>514.037</v>
+        <v>362.016</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2.959</v>
+        <v>5.513</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2956.414</v>
+        <v>348.261</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>0.418</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>2959.373</v>
+        <v>354.192</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0</v>
@@ -788,7 +788,7 @@
         <v>5</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>20065.2718598</v>
+        <v>0.00045865351993</v>
       </c>
       <c r="O5" s="2" t="b">
         <v>1</v>
@@ -820,22 +820,22 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>533.158</v>
+        <v>388.043</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>8.364000000000001</v>
+        <v>6.215</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>5404.204</v>
+        <v>354.109</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
+        <v>0.298</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>5412.568</v>
+        <v>360.622</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0</v>
@@ -850,7 +850,7 @@
         <v>5</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3019459.54439</v>
+        <v>1065.89600956</v>
       </c>
       <c r="O6" s="2" t="b">
         <v>1</v>
